--- a/output/quickfixpro_all_markets_daily.xlsx
+++ b/output/quickfixpro_all_markets_daily.xlsx
@@ -582,10 +582,10 @@
         <v>77.8</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30.62</v>
+        <v>19.05</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>130620.04</v>
+        <v>119053.36</v>
       </c>
     </row>
     <row r="3">
@@ -630,10 +630,10 @@
         <v>66.7</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>22.82</v>
+        <v>11.39</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>122823.77</v>
+        <v>111388.35</v>
       </c>
     </row>
     <row r="4">
@@ -678,10 +678,10 @@
         <v>100</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>22.06</v>
+        <v>10.8</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>122056.76</v>
+        <v>110805</v>
       </c>
     </row>
     <row r="5">
@@ -726,10 +726,10 @@
         <v>66.7</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>15.92</v>
+        <v>8.26</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>115915.98</v>
+        <v>108255.39</v>
       </c>
     </row>
     <row r="6">
@@ -774,10 +774,10 @@
         <v>100</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13.66</v>
+        <v>6.85</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>113662.64</v>
+        <v>106848.06</v>
       </c>
     </row>
     <row r="7">
@@ -822,10 +822,10 @@
         <v>100</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13.09</v>
+        <v>6.57</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>113094.92</v>
+        <v>106569.95</v>
       </c>
     </row>
     <row r="8">
@@ -870,10 +870,10 @@
         <v>33.3</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9.76</v>
+        <v>5.06</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>109762.65</v>
+        <v>105062.25</v>
       </c>
     </row>
     <row r="9">
@@ -918,10 +918,10 @@
         <v>50</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9.74</v>
+        <v>4.97</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>109735.25</v>
+        <v>104969.43</v>
       </c>
     </row>
     <row r="10">
@@ -966,10 +966,10 @@
         <v>75</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7.71</v>
+        <v>4.07</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>107713.69</v>
+        <v>104069.63</v>
       </c>
     </row>
     <row r="11">
@@ -1014,10 +1014,10 @@
         <v>100</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5.68</v>
+        <v>2.89</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>105677.3</v>
+        <v>102887.37</v>
       </c>
     </row>
     <row r="12">
@@ -1062,10 +1062,10 @@
         <v>50</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4.03</v>
+        <v>2.09</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>104033.48</v>
+        <v>102087.27</v>
       </c>
     </row>
     <row r="13">
@@ -1110,10 +1110,10 @@
         <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.19</v>
+        <v>1.18</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102188.52</v>
+        <v>101182.61</v>
       </c>
     </row>
     <row r="14">
@@ -1158,10 +1158,10 @@
         <v>100</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1.72</v>
+        <v>0.88</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>101721.8</v>
+        <v>100875.68</v>
       </c>
     </row>
     <row r="15">
@@ -1206,10 +1206,10 @@
         <v>50</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1.55</v>
+        <v>0.8</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>101553.87</v>
+        <v>100802.76</v>
       </c>
     </row>
     <row r="16">
@@ -1254,10 +1254,10 @@
         <v>100</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1.03</v>
+        <v>0.52</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>101028.5</v>
+        <v>100523.08</v>
       </c>
     </row>
     <row r="17">
@@ -1302,10 +1302,10 @@
         <v>50</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>100488.82</v>
+        <v>100256.84</v>
       </c>
     </row>
     <row r="18">
@@ -1350,10 +1350,10 @@
         <v>50</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>100199.64</v>
+        <v>100108.61</v>
       </c>
     </row>
     <row r="19">
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>-1.57</v>
+        <v>-0.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="26">
@@ -1716,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-3.12</v>
+        <v>-1.59</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>96878.74000000001</v>
+        <v>98406.39999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1768,10 +1768,10 @@
         <v>100</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>16.61</v>
+        <v>11.59</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>116613.62</v>
+        <v>111586.39</v>
       </c>
     </row>
     <row r="28">
@@ -1820,10 +1820,10 @@
         <v>75</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>12.19</v>
+        <v>6.12</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>112193.07</v>
+        <v>106121.53</v>
       </c>
     </row>
     <row r="29">
@@ -1872,10 +1872,10 @@
         <v>75</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>10.13</v>
+        <v>5.1</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>110132.23</v>
+        <v>105100.55</v>
       </c>
     </row>
     <row r="30">
@@ -1924,10 +1924,10 @@
         <v>66.7</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>8.94</v>
+        <v>4.52</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>108936.51</v>
+        <v>104522.09</v>
       </c>
     </row>
     <row r="31">
@@ -1976,16 +1976,16 @@
         <v>100</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>7.37</v>
+        <v>3.9</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>107366.62</v>
+        <v>103897.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -2004,34 +2004,34 @@
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>20</v>
+        <v>66.7</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.68</v>
+        <v>0.21</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>100683.19</v>
+        <v>100211.77</v>
       </c>
     </row>
     <row r="33">
@@ -2430,16 +2430,16 @@
         <v>50</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>99881.71000000001</v>
+        <v>99945.64999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2461,16 +2461,16 @@
         <v>73</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="6" t="n">
         <v>0</v>
@@ -2479,19 +2479,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-1.57</v>
+        <v>-0.83</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>98427</v>
+        <v>99170.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2510,40 +2510,40 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-1.6</v>
+        <v>-0.84</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>98402.64999999999</v>
+        <v>99155.56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.573%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 08:50 UTC.</t>
+          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 09:49 UTC.</t>
         </is>
       </c>
     </row>
@@ -2703,13 +2703,13 @@
         <v>-1</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N2" t="n">
         <v>100000</v>
       </c>
       <c r="O2" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="3">
@@ -2760,13 +2760,13 @@
         <v>3.5407</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5.5695</v>
+        <v>2.8326</v>
       </c>
       <c r="N3" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O3" t="n">
-        <v>103908.89</v>
+        <v>102009.89</v>
       </c>
     </row>
     <row r="4">
@@ -2817,13 +2817,13 @@
         <v>2.8416</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4.4699</v>
+        <v>2.2733</v>
       </c>
       <c r="N4" t="n">
-        <v>103908.89</v>
+        <v>102009.89</v>
       </c>
       <c r="O4" t="n">
-        <v>108553.5</v>
+        <v>104328.88</v>
       </c>
     </row>
     <row r="5">
@@ -2874,13 +2874,13 @@
         <v>0.9246</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1.4543</v>
+        <v>0.7396</v>
       </c>
       <c r="N5" t="n">
-        <v>108553.5</v>
+        <v>104328.88</v>
       </c>
       <c r="O5" t="n">
-        <v>110132.23</v>
+        <v>105100.55</v>
       </c>
     </row>
     <row r="6">
@@ -2931,13 +2931,13 @@
         <v>5.4444</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.5641</v>
+        <v>4.3556</v>
       </c>
       <c r="N6" t="n">
         <v>100000</v>
       </c>
       <c r="O6" t="n">
-        <v>108564.11</v>
+        <v>104355.56</v>
       </c>
     </row>
     <row r="7">
@@ -2988,13 +2988,13 @@
         <v>2.9856</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.6963</v>
+        <v>2.3885</v>
       </c>
       <c r="N7" t="n">
-        <v>108564.11</v>
+        <v>104355.56</v>
       </c>
       <c r="O7" t="n">
-        <v>113662.64</v>
+        <v>106848.06</v>
       </c>
     </row>
     <row r="8">
@@ -3045,13 +3045,13 @@
         <v>1.1798</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1.8558</v>
+        <v>0.9438</v>
       </c>
       <c r="N8" t="n">
         <v>100000</v>
       </c>
       <c r="O8" t="n">
-        <v>101855.79</v>
+        <v>100943.82</v>
       </c>
     </row>
     <row r="9">
@@ -3102,13 +3102,13 @@
         <v>4.2329</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.6583</v>
+        <v>3.3863</v>
       </c>
       <c r="N9" t="n">
-        <v>101855.79</v>
+        <v>100943.82</v>
       </c>
       <c r="O9" t="n">
-        <v>108637.67</v>
+        <v>104362.08</v>
       </c>
     </row>
     <row r="10">
@@ -3159,13 +3159,13 @@
         <v>2.0606</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3.2413</v>
+        <v>1.6485</v>
       </c>
       <c r="N10" t="n">
-        <v>108637.67</v>
+        <v>104362.08</v>
       </c>
       <c r="O10" t="n">
-        <v>112158.97</v>
+        <v>106082.48</v>
       </c>
     </row>
     <row r="11">
@@ -3216,13 +3216,13 @@
         <v>4.0732</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6.4071</v>
+        <v>3.2585</v>
       </c>
       <c r="N11" t="n">
-        <v>112158.97</v>
+        <v>106082.48</v>
       </c>
       <c r="O11" t="n">
-        <v>119345.11</v>
+        <v>109539.21</v>
       </c>
     </row>
     <row r="12">
@@ -3273,13 +3273,13 @@
         <v>1.4444</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2.2721</v>
+        <v>1.1556</v>
       </c>
       <c r="N12" t="n">
-        <v>119345.11</v>
+        <v>109539.21</v>
       </c>
       <c r="O12" t="n">
-        <v>122056.76</v>
+        <v>110805</v>
       </c>
     </row>
     <row r="13">
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>122056.76</v>
+        <v>110805</v>
       </c>
       <c r="O13" t="n">
-        <v>122056.76</v>
+        <v>110805</v>
       </c>
     </row>
     <row r="14">
@@ -3370,13 +3370,13 @@
         <v>-1</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N14" t="n">
         <v>100000</v>
       </c>
       <c r="O14" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="15">
@@ -3427,13 +3427,13 @@
         <v>0.9802999999999999</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1.542</v>
+        <v>0.7842</v>
       </c>
       <c r="N15" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O15" t="n">
-        <v>99944.7</v>
+        <v>99977.94</v>
       </c>
     </row>
     <row r="16">
@@ -3484,13 +3484,13 @@
         <v>3.4394</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5.4102</v>
+        <v>2.7515</v>
       </c>
       <c r="N16" t="n">
-        <v>99944.7</v>
+        <v>99977.94</v>
       </c>
       <c r="O16" t="n">
-        <v>105351.87</v>
+        <v>102728.84</v>
       </c>
     </row>
     <row r="17">
@@ -3541,13 +3541,13 @@
         <v>4.1282</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6.4937</v>
+        <v>3.3026</v>
       </c>
       <c r="N17" t="n">
-        <v>105351.87</v>
+        <v>102728.84</v>
       </c>
       <c r="O17" t="n">
-        <v>112193.07</v>
+        <v>106121.53</v>
       </c>
     </row>
     <row r="18">
@@ -3598,13 +3598,13 @@
         <v>-1</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N18" t="n">
         <v>100000</v>
       </c>
       <c r="O18" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="19">
@@ -3655,13 +3655,13 @@
         <v>0.9396</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1.478</v>
+        <v>0.7517</v>
       </c>
       <c r="N19" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O19" t="n">
-        <v>99881.71000000001</v>
+        <v>99945.64999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3712,13 +3712,13 @@
         <v>-1</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N20" t="n">
         <v>100000</v>
       </c>
       <c r="O20" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="21">
@@ -3769,13 +3769,13 @@
         <v>8.454499999999999</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13.299</v>
+        <v>6.7636</v>
       </c>
       <c r="N21" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O21" t="n">
-        <v>111516.81</v>
+        <v>105909.53</v>
       </c>
     </row>
     <row r="22">
@@ -3826,13 +3826,13 @@
         <v>-1</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N22" t="n">
-        <v>111516.81</v>
+        <v>105909.53</v>
       </c>
       <c r="O22" t="n">
-        <v>109762.65</v>
+        <v>105062.25</v>
       </c>
     </row>
     <row r="23">
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>109762.65</v>
+        <v>105062.25</v>
       </c>
       <c r="O23" t="n">
-        <v>109762.65</v>
+        <v>105062.25</v>
       </c>
     </row>
     <row r="24">
@@ -3923,13 +3923,13 @@
         <v>5.4262</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8.535500000000001</v>
+        <v>4.341</v>
       </c>
       <c r="N24" t="n">
         <v>100000</v>
       </c>
       <c r="O24" t="n">
-        <v>108535.46</v>
+        <v>104340.98</v>
       </c>
     </row>
     <row r="25">
@@ -3980,13 +3980,13 @@
         <v>9.5189</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>14.9732</v>
+        <v>7.6151</v>
       </c>
       <c r="N25" t="n">
-        <v>108535.46</v>
+        <v>104340.98</v>
       </c>
       <c r="O25" t="n">
-        <v>124786.67</v>
+        <v>112286.65</v>
       </c>
     </row>
     <row r="26">
@@ -4037,13 +4037,13 @@
         <v>-1</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N26" t="n">
-        <v>124786.67</v>
+        <v>112286.65</v>
       </c>
       <c r="O26" t="n">
-        <v>122823.77</v>
+        <v>111388.35</v>
       </c>
     </row>
     <row r="27">
@@ -4091,13 +4091,13 @@
         <v>-1</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N27" t="n">
         <v>100000</v>
       </c>
       <c r="O27" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="28">
@@ -4148,13 +4148,13 @@
         <v>1.1449</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1.801</v>
+        <v>0.9159</v>
       </c>
       <c r="N28" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O28" t="n">
-        <v>100199.64</v>
+        <v>100108.61</v>
       </c>
     </row>
     <row r="29">
@@ -4205,13 +4205,13 @@
         <v>2.3372</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3.6765</v>
+        <v>1.8698</v>
       </c>
       <c r="N29" t="n">
         <v>100000</v>
       </c>
       <c r="O29" t="n">
-        <v>103676.46</v>
+        <v>101869.78</v>
       </c>
     </row>
     <row r="30">
@@ -4251,7 +4251,7 @@
         <v>6045.97</v>
       </c>
       <c r="J30" t="n">
-        <v>6045.97</v>
+        <v>6041.78</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4259,16 +4259,16 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0.7896</v>
+        <v>1.0216</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.242</v>
+        <v>0.8173</v>
       </c>
       <c r="N30" t="n">
-        <v>103676.46</v>
+        <v>101869.78</v>
       </c>
       <c r="O30" t="n">
-        <v>104964.15</v>
+        <v>102702.34</v>
       </c>
     </row>
     <row r="31">
@@ -4319,13 +4319,13 @@
         <v>1.4551</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2.2888</v>
+        <v>1.1641</v>
       </c>
       <c r="N31" t="n">
-        <v>104964.15</v>
+        <v>102702.34</v>
       </c>
       <c r="O31" t="n">
-        <v>107366.62</v>
+        <v>103897.86</v>
       </c>
     </row>
     <row r="32">
@@ -4376,13 +4376,13 @@
         <v>-1</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N32" t="n">
         <v>100000</v>
       </c>
       <c r="O32" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="33">
@@ -4433,13 +4433,13 @@
         <v>2.6842</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4.2223</v>
+        <v>2.1474</v>
       </c>
       <c r="N33" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O33" t="n">
-        <v>102582.85</v>
+        <v>101330.19</v>
       </c>
     </row>
     <row r="34">
@@ -4490,13 +4490,13 @@
         <v>3.9375</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6.1937</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>102582.85</v>
+        <v>101330.19</v>
       </c>
       <c r="O34" t="n">
-        <v>108936.51</v>
+        <v>104522.09</v>
       </c>
     </row>
     <row r="35">
@@ -4536,7 +4536,7 @@
         <v>127.15</v>
       </c>
       <c r="J35" t="n">
-        <v>127.15</v>
+        <v>127.13</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.3913</v>
+        <v>1.4783</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2.1885</v>
+        <v>1.1826</v>
       </c>
       <c r="N35" t="n">
         <v>100000</v>
       </c>
       <c r="O35" t="n">
-        <v>102188.52</v>
+        <v>101182.61</v>
       </c>
     </row>
     <row r="36">
@@ -4593,7 +4593,7 @@
         <v>4337.9</v>
       </c>
       <c r="J36" t="n">
-        <v>4337.9</v>
+        <v>4258.5</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4601,16 +4601,16 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.3193</v>
+        <v>8.102399999999999</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5.2212</v>
+        <v>6.4819</v>
       </c>
       <c r="N36" t="n">
         <v>100000</v>
       </c>
       <c r="O36" t="n">
-        <v>105221.22</v>
+        <v>106481.93</v>
       </c>
     </row>
     <row r="37">
@@ -4661,13 +4661,13 @@
         <v>1.9674</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3.0947</v>
+        <v>1.5739</v>
       </c>
       <c r="N37" t="n">
-        <v>105221.22</v>
+        <v>106481.93</v>
       </c>
       <c r="O37" t="n">
-        <v>108477.51</v>
+        <v>108157.86</v>
       </c>
     </row>
     <row r="38">
@@ -4718,13 +4718,13 @@
         <v>1.1209</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.7632</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>108477.51</v>
+        <v>108157.86</v>
       </c>
       <c r="O38" t="n">
-        <v>110390.15</v>
+        <v>109127.73</v>
       </c>
     </row>
     <row r="39">
@@ -4775,13 +4775,13 @@
         <v>5.2326</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8.2309</v>
+        <v>4.1861</v>
       </c>
       <c r="N39" t="n">
-        <v>110390.15</v>
+        <v>109127.73</v>
       </c>
       <c r="O39" t="n">
-        <v>119476.3</v>
+        <v>113695.94</v>
       </c>
     </row>
     <row r="40">
@@ -4829,13 +4829,13 @@
         <v>-1</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N40" t="n">
-        <v>119476.3</v>
+        <v>113695.94</v>
       </c>
       <c r="O40" t="n">
-        <v>117596.93</v>
+        <v>112786.37</v>
       </c>
     </row>
     <row r="41">
@@ -4883,13 +4883,13 @@
         <v>-1</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N41" t="n">
-        <v>117596.93</v>
+        <v>112786.37</v>
       </c>
       <c r="O41" t="n">
-        <v>115747.14</v>
+        <v>111884.08</v>
       </c>
     </row>
     <row r="42">
@@ -4940,13 +4940,13 @@
         <v>2.4323</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3.8261</v>
+        <v>1.9459</v>
       </c>
       <c r="N42" t="n">
-        <v>115747.14</v>
+        <v>111884.08</v>
       </c>
       <c r="O42" t="n">
-        <v>120175.7</v>
+        <v>114061.2</v>
       </c>
     </row>
     <row r="43">
@@ -4997,13 +4997,13 @@
         <v>3.2822</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5.1629</v>
+        <v>2.6258</v>
       </c>
       <c r="N43" t="n">
-        <v>120175.7</v>
+        <v>114061.2</v>
       </c>
       <c r="O43" t="n">
-        <v>126380.31</v>
+        <v>117056.2</v>
       </c>
     </row>
     <row r="44">
@@ -5054,13 +5054,13 @@
         <v>2.1327</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3.3547</v>
+        <v>1.7062</v>
       </c>
       <c r="N44" t="n">
-        <v>126380.31</v>
+        <v>117056.2</v>
       </c>
       <c r="O44" t="n">
-        <v>130620.04</v>
+        <v>119053.36</v>
       </c>
     </row>
     <row r="45">
@@ -5111,13 +5111,13 @@
         <v>1.0946</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.7218</v>
+        <v>0.8757</v>
       </c>
       <c r="N45" t="n">
         <v>100000</v>
       </c>
       <c r="O45" t="n">
-        <v>101721.8</v>
+        <v>100875.68</v>
       </c>
     </row>
     <row r="46">
@@ -5165,13 +5165,13 @@
         <v>-1</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N46" t="n">
         <v>100000</v>
       </c>
       <c r="O46" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="47">
@@ -5222,13 +5222,13 @@
         <v>6.1212</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>9.6287</v>
+        <v>4.897</v>
       </c>
       <c r="N47" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O47" t="n">
-        <v>107904.21</v>
+        <v>104057.79</v>
       </c>
     </row>
     <row r="48">
@@ -5279,13 +5279,13 @@
         <v>2.112</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3.3222</v>
+        <v>1.6896</v>
       </c>
       <c r="N48" t="n">
-        <v>107904.21</v>
+        <v>104057.79</v>
       </c>
       <c r="O48" t="n">
-        <v>111488.98</v>
+        <v>105815.95</v>
       </c>
     </row>
     <row r="49">
@@ -5336,13 +5336,13 @@
         <v>-1</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N49" t="n">
-        <v>111488.98</v>
+        <v>105815.95</v>
       </c>
       <c r="O49" t="n">
-        <v>109735.25</v>
+        <v>104969.43</v>
       </c>
     </row>
     <row r="50">
@@ -5393,13 +5393,13 @@
         <v>-1</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N50" t="n">
         <v>100000</v>
       </c>
       <c r="O50" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="51">
@@ -5450,13 +5450,13 @@
         <v>-1</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N51" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O51" t="n">
-        <v>96878.74000000001</v>
+        <v>98406.39999999999</v>
       </c>
     </row>
     <row r="52">
@@ -5507,13 +5507,13 @@
         <v>4.0326</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6.3433</v>
+        <v>3.2261</v>
       </c>
       <c r="N52" t="n">
-        <v>96878.74000000001</v>
+        <v>98406.39999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>103024.1</v>
+        <v>101581.1</v>
       </c>
     </row>
     <row r="53">
@@ -5564,13 +5564,13 @@
         <v>0.6229</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.9798</v>
+        <v>0.4983</v>
       </c>
       <c r="N53" t="n">
-        <v>103024.1</v>
+        <v>101581.1</v>
       </c>
       <c r="O53" t="n">
-        <v>104033.48</v>
+        <v>102087.27</v>
       </c>
     </row>
     <row r="54">
@@ -5621,13 +5621,13 @@
         <v>-1</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N54" t="n">
         <v>100000</v>
       </c>
       <c r="O54" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="55">
@@ -5678,13 +5678,13 @@
         <v>2.0196</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3.1768</v>
+        <v>1.6157</v>
       </c>
       <c r="N55" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O55" t="n">
-        <v>101553.87</v>
+        <v>100802.76</v>
       </c>
     </row>
     <row r="56">
@@ -5735,13 +5735,13 @@
         <v>2.6882</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4.2286</v>
+        <v>2.1506</v>
       </c>
       <c r="N56" t="n">
         <v>100000</v>
       </c>
       <c r="O56" t="n">
-        <v>104228.59</v>
+        <v>102150.59</v>
       </c>
     </row>
     <row r="57">
@@ -5792,13 +5792,13 @@
         <v>5.4079</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8.506600000000001</v>
+        <v>4.3263</v>
       </c>
       <c r="N57" t="n">
-        <v>104228.59</v>
+        <v>102150.59</v>
       </c>
       <c r="O57" t="n">
-        <v>113094.92</v>
+        <v>106569.95</v>
       </c>
     </row>
     <row r="58">
@@ -5838,7 +5838,7 @@
         <v>2032.3</v>
       </c>
       <c r="J58" t="n">
-        <v>2032.3</v>
+        <v>2031.1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5846,16 +5846,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.7973</v>
+        <v>1.8385</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.8271</v>
+        <v>1.4708</v>
       </c>
       <c r="N58" t="n">
         <v>100000</v>
       </c>
       <c r="O58" t="n">
-        <v>102827.08</v>
+        <v>101470.79</v>
       </c>
     </row>
     <row r="59">
@@ -5906,13 +5906,13 @@
         <v>-1</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N59" t="n">
-        <v>102827.08</v>
+        <v>101470.79</v>
       </c>
       <c r="O59" t="n">
-        <v>101209.61</v>
+        <v>100659.02</v>
       </c>
     </row>
     <row r="60">
@@ -5952,7 +5952,7 @@
         <v>1613.1</v>
       </c>
       <c r="J60" t="n">
-        <v>1613.1</v>
+        <v>1618.8</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5960,16 +5960,16 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.9322</v>
+        <v>1.1003</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1.4663</v>
+        <v>0.8802</v>
       </c>
       <c r="N60" t="n">
-        <v>101209.61</v>
+        <v>100659.02</v>
       </c>
       <c r="O60" t="n">
-        <v>102693.62</v>
+        <v>101545.06</v>
       </c>
     </row>
     <row r="61">
@@ -6020,13 +6020,13 @@
         <v>3.1077</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4.8884</v>
+        <v>2.4862</v>
       </c>
       <c r="N61" t="n">
-        <v>102693.62</v>
+        <v>101545.06</v>
       </c>
       <c r="O61" t="n">
-        <v>107713.69</v>
+        <v>104069.63</v>
       </c>
     </row>
     <row r="62">
@@ -6077,13 +6077,13 @@
         <v>-1</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N62" t="n">
         <v>100000</v>
       </c>
       <c r="O62" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="63">
@@ -6134,13 +6134,13 @@
         <v>3.6092</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5.6773</v>
+        <v>2.8874</v>
       </c>
       <c r="N63" t="n">
         <v>100000</v>
       </c>
       <c r="O63" t="n">
-        <v>105677.3</v>
+        <v>102887.37</v>
       </c>
     </row>
     <row r="64">
@@ -6180,7 +6180,7 @@
         <v>6919.18</v>
       </c>
       <c r="J64" t="n">
-        <v>6919.18</v>
+        <v>6914.11</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6188,16 +6188,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.6252</v>
+        <v>5.2382</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7.2754</v>
+        <v>4.1906</v>
       </c>
       <c r="N64" t="n">
         <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>107275.36</v>
+        <v>104190.57</v>
       </c>
     </row>
     <row r="65">
@@ -6237,7 +6237,7 @@
         <v>6958.82</v>
       </c>
       <c r="J65" t="n">
-        <v>6988.83</v>
+        <v>7002</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6245,16 +6245,16 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>-1</v>
+        <v>-3.0482</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>-1.573</v>
+        <v>-2.4386</v>
       </c>
       <c r="N65" t="n">
-        <v>107275.36</v>
+        <v>104190.57</v>
       </c>
       <c r="O65" t="n">
-        <v>105587.92</v>
+        <v>101649.81</v>
       </c>
     </row>
     <row r="66">
@@ -6302,13 +6302,13 @@
         <v>-1</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N66" t="n">
-        <v>105587.92</v>
+        <v>101649.81</v>
       </c>
       <c r="O66" t="n">
-        <v>103927.02</v>
+        <v>100836.61</v>
       </c>
     </row>
     <row r="67">
@@ -6356,13 +6356,13 @@
         <v>-1</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N67" t="n">
-        <v>103927.02</v>
+        <v>100836.61</v>
       </c>
       <c r="O67" t="n">
-        <v>102292.25</v>
+        <v>100029.92</v>
       </c>
     </row>
     <row r="68">
@@ -6402,7 +6402,7 @@
         <v>6870.44</v>
       </c>
       <c r="J68" t="n">
-        <v>6770.77</v>
+        <v>6769.03</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6410,16 +6410,16 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-1</v>
+        <v>-1.0736</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8589</v>
       </c>
       <c r="N68" t="n">
-        <v>102292.25</v>
+        <v>100029.92</v>
       </c>
       <c r="O68" t="n">
-        <v>100683.19</v>
+        <v>99170.75</v>
       </c>
     </row>
     <row r="69">
@@ -6470,13 +6470,13 @@
         <v>-1</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N69" t="n">
         <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="70">
@@ -6527,13 +6527,13 @@
         <v>1.3317</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2.0948</v>
+        <v>1.0654</v>
       </c>
       <c r="N70" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O70" t="n">
-        <v>100488.82</v>
+        <v>100256.84</v>
       </c>
     </row>
     <row r="71">
@@ -6584,13 +6584,13 @@
         <v>0.6538</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1.0285</v>
+        <v>0.5231</v>
       </c>
       <c r="N71" t="n">
         <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>101028.5</v>
+        <v>100523.08</v>
       </c>
     </row>
     <row r="72">
@@ -6630,7 +6630,7 @@
         <v>20.76</v>
       </c>
       <c r="J72" t="n">
-        <v>21.07</v>
+        <v>21.08</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6638,16 +6638,16 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-1</v>
+        <v>-1.0556</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8444</v>
       </c>
       <c r="N72" t="n">
         <v>100000</v>
       </c>
       <c r="O72" t="n">
-        <v>98427</v>
+        <v>99155.56</v>
       </c>
     </row>
     <row r="73">
@@ -6698,13 +6698,13 @@
         <v>-1</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N73" t="n">
         <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="74">
@@ -6743,22 +6743,25 @@
       <c r="I74" t="n">
         <v>0.8602</v>
       </c>
+      <c r="J74" t="n">
+        <v>0.8602</v>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_bar</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v>-1.573</v>
+        <v>0.2727</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>0.2182</v>
       </c>
       <c r="N74" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O74" t="n">
-        <v>96878.74000000001</v>
+        <v>99416.44</v>
       </c>
     </row>
     <row r="75">
@@ -6809,13 +6812,13 @@
         <v>1</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1.573</v>
+        <v>0.8</v>
       </c>
       <c r="N75" t="n">
-        <v>96878.74000000001</v>
+        <v>99416.44</v>
       </c>
       <c r="O75" t="n">
-        <v>98402.64999999999</v>
+        <v>100211.77</v>
       </c>
     </row>
     <row r="76">
@@ -6866,13 +6869,13 @@
         <v>-1</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N76" t="n">
         <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
     </row>
     <row r="77">
@@ -6923,13 +6926,13 @@
         <v>-1</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N77" t="n">
-        <v>98427</v>
+        <v>99200</v>
       </c>
       <c r="O77" t="n">
-        <v>96878.74000000001</v>
+        <v>98406.39999999999</v>
       </c>
     </row>
     <row r="78">
@@ -6980,13 +6983,13 @@
         <v>1.1918</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1.8748</v>
+        <v>0.9535</v>
       </c>
       <c r="N78" t="n">
         <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>101874.76</v>
+        <v>100953.47</v>
       </c>
     </row>
     <row r="79">
@@ -7037,13 +7040,13 @@
         <v>2.0286</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>3.1909</v>
+        <v>1.6229</v>
       </c>
       <c r="N79" t="n">
-        <v>101874.76</v>
+        <v>100953.47</v>
       </c>
       <c r="O79" t="n">
-        <v>105125.52</v>
+        <v>102591.8</v>
       </c>
     </row>
     <row r="80">
@@ -7094,13 +7097,13 @@
         <v>2.5744</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4.0495</v>
+        <v>2.0595</v>
       </c>
       <c r="N80" t="n">
-        <v>105125.52</v>
+        <v>102591.8</v>
       </c>
       <c r="O80" t="n">
-        <v>109382.55</v>
+        <v>104704.66</v>
       </c>
     </row>
     <row r="81">
@@ -7151,13 +7154,13 @@
         <v>-1</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N81" t="n">
-        <v>109382.55</v>
+        <v>104704.66</v>
       </c>
       <c r="O81" t="n">
-        <v>107661.96</v>
+        <v>103867.03</v>
       </c>
     </row>
     <row r="82">
@@ -7208,13 +7211,13 @@
         <v>1.9407</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3.0528</v>
+        <v>1.5526</v>
       </c>
       <c r="N82" t="n">
-        <v>107661.96</v>
+        <v>103867.03</v>
       </c>
       <c r="O82" t="n">
-        <v>110948.65</v>
+        <v>105479.66</v>
       </c>
     </row>
     <row r="83">
@@ -7254,7 +7257,7 @@
         <v>99.56399999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>99.56399999999999</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7262,16 +7265,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.008</v>
+        <v>2.424</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3.1586</v>
+        <v>1.9392</v>
       </c>
       <c r="N83" t="n">
-        <v>110948.65</v>
+        <v>105479.66</v>
       </c>
       <c r="O83" t="n">
-        <v>114453.05</v>
+        <v>107525.12</v>
       </c>
     </row>
     <row r="84">
@@ -7322,13 +7325,13 @@
         <v>-1</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N84" t="n">
-        <v>114453.05</v>
+        <v>107525.12</v>
       </c>
       <c r="O84" t="n">
-        <v>112652.71</v>
+        <v>106664.92</v>
       </c>
     </row>
     <row r="85">
@@ -7379,13 +7382,13 @@
         <v>-1</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>-1.573</v>
+        <v>-0.8</v>
       </c>
       <c r="N85" t="n">
-        <v>112652.71</v>
+        <v>106664.92</v>
       </c>
       <c r="O85" t="n">
-        <v>110880.68</v>
+        <v>105811.6</v>
       </c>
     </row>
     <row r="86">
@@ -7436,13 +7439,13 @@
         <v>2.887</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>4.5412</v>
+        <v>2.3096</v>
       </c>
       <c r="N86" t="n">
-        <v>110880.68</v>
+        <v>105811.6</v>
       </c>
       <c r="O86" t="n">
-        <v>115915.98</v>
+        <v>108255.39</v>
       </c>
     </row>
     <row r="87">
@@ -7482,7 +7485,7 @@
         <v>118.32</v>
       </c>
       <c r="J87" t="n">
-        <v>118.32</v>
+        <v>113.29</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7490,16 +7493,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.5954</v>
+        <v>6.4351</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4.0826</v>
+        <v>5.1481</v>
       </c>
       <c r="N87" t="n">
         <v>100000</v>
       </c>
       <c r="O87" t="n">
-        <v>104082.6</v>
+        <v>105148.09</v>
       </c>
     </row>
     <row r="88">
@@ -7550,13 +7553,13 @@
         <v>7.6538</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>12.0395</v>
+        <v>6.1231</v>
       </c>
       <c r="N88" t="n">
-        <v>104082.6</v>
+        <v>105148.09</v>
       </c>
       <c r="O88" t="n">
-        <v>116613.62</v>
+        <v>111586.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/quickfixpro_all_markets_daily.xlsx
+++ b/output/quickfixpro_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 09:49 UTC.</t>
+          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 19:13 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixpro_all_markets_daily.xlsx
+++ b/output/quickfixpro_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 19:13 UTC.</t>
+          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 20:58 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixpro_all_markets_daily.xlsx
+++ b/output/quickfixpro_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 20:58 UTC.</t>
+          <t>quickfixpro daily (target = one tick beyond the entry bar's own extreme (a short: below its low)), starting capital 100,000, risk 1.175%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-24); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-27 23:07 UTC.</t>
         </is>
       </c>
     </row>
